--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MISSISSIPPI_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MISSISSIPPI_2012.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C107">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C490">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C566">
